--- a/themes/mortgage.xlsx
+++ b/themes/mortgage.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,61 +450,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Подать заявку на ипотечный кредит вы можете по [ссылке]({{$temp.MortgageLink}})'</t>
+          <t xml:space="preserve">  Более подробные условия и ответы на частозадаваемые вопросы вы сможете найти по [ссылке]({{$temp.MortgageLink}})</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Подать заявку на ипотечный кредит вы можете по [ссылке]({{$temp.MortgageLink}}).'</t>
+          <t xml:space="preserve">  Более подробные условия и ответы на часто задаваемые вопросы вы сможете найти по [ссылке]({{$temp.MortgageLink}})</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -  Оставить заявку на рассмотрение и ознакомиться со всеми ипотечными программами и услугами можно по [ссылке]({{$temp.link["MortgageLink"]}})</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -  Оставить заявку на рассмотрение и ознакомиться со всеми ипотечными программами и услугами можно по [ссылке]({{$temp.link["MortgageLink"]}}).</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Более подробные условия и ответы на частозадаваемые вопросы вы сможете найти по [ссылке]({{$temp.MortgageLink}})</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Более подробные условия и ответы на часто задаваемые вопросы вы сможете найти по [ссылке]({{$temp.MortgageLink}}).</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>«частозадаваемые» исправлено на «часто задаваемые» (пишется раздельно); добавлена точка в конце предложения</t>
+          <t>«частозадаваемые» исправлено на «часто задаваемые» (пишется раздельно)</t>
         </is>
       </c>
     </row>
